--- a/Collections/United_Kingdom/#United_Kingdom#Before_DecimalDay#Regular#[1953-1970]#circulation_quality.xlsx
+++ b/Collections/United_Kingdom/#United_Kingdom#Before_DecimalDay#Regular#[1953-1970]#circulation_quality.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\United_Kingdom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{369E5897-FE43-4B5C-BA21-E0481328900B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD4E8E68-7039-4C29-B13D-E8B1BAC762D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="farthing" sheetId="38" r:id="rId1"/>
@@ -43,6 +43,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1150,18 +1153,18 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1748,14 +1751,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="24"/>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="27"/>
+      <c r="D1" s="29"/>
       <c r="E1" s="8" t="s">
         <v>5</v>
       </c>
@@ -1764,8 +1767,8 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="28"/>
-      <c r="B2" s="29" t="s">
+      <c r="A2" s="27"/>
+      <c r="B2" s="25" t="s">
         <v>149</v>
       </c>
       <c r="C2" s="9" t="s">
@@ -2228,7 +2231,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:D1"/>
   </mergeCells>
-  <conditionalFormatting sqref="F3 F5">
+  <conditionalFormatting sqref="F5 F3">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2245,7 +2248,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4 F6">
+  <conditionalFormatting sqref="F6 F4">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2282,14 +2285,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="24"/>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="27"/>
+      <c r="D1" s="29"/>
       <c r="E1" s="8" t="s">
         <v>5</v>
       </c>
@@ -2298,8 +2301,8 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="28"/>
-      <c r="B2" s="29" t="s">
+      <c r="A2" s="27"/>
+      <c r="B2" s="25" t="s">
         <v>149</v>
       </c>
       <c r="C2" s="9" t="s">
@@ -2428,7 +2431,7 @@
         <v>32</v>
       </c>
       <c r="F7" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="5" t="str">
         <f t="shared" si="0"/>
@@ -2500,7 +2503,7 @@
         <v>35</v>
       </c>
       <c r="F10" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="5" t="str">
         <f t="shared" si="0"/>
@@ -2753,7 +2756,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:D1"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5 F3 F7 F9 F13 F15 F17">
+  <conditionalFormatting sqref="F3 F5 F7 F9 F13 F15 F17">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2770,7 +2773,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6 F4 F8 F10 F12 F14 F16">
+  <conditionalFormatting sqref="F4 F6 F8 F10 F12 F14 F16">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2824,14 +2827,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="24"/>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="27"/>
+      <c r="D1" s="29"/>
       <c r="E1" s="8" t="s">
         <v>5</v>
       </c>
@@ -2840,8 +2843,8 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="28"/>
-      <c r="B2" s="29" t="s">
+      <c r="A2" s="27"/>
+      <c r="B2" s="25" t="s">
         <v>149</v>
       </c>
       <c r="C2" s="9" t="s">
@@ -3247,7 +3250,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:D1"/>
   </mergeCells>
-  <conditionalFormatting sqref="F11 F3 F13 F15 F17">
+  <conditionalFormatting sqref="F3 F11 F13 F15 F17">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3264,7 +3267,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14 F12 F16">
+  <conditionalFormatting sqref="F12 F14 F16">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3301,14 +3304,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="24"/>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="27"/>
+      <c r="D1" s="29"/>
       <c r="E1" s="8" t="s">
         <v>5</v>
       </c>
@@ -3317,8 +3320,8 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="28"/>
-      <c r="B2" s="29" t="s">
+      <c r="A2" s="27"/>
+      <c r="B2" s="25" t="s">
         <v>149</v>
       </c>
       <c r="C2" s="9" t="s">
@@ -3423,7 +3426,7 @@
         <v>55</v>
       </c>
       <c r="F6" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3543,7 +3546,7 @@
         <v>60</v>
       </c>
       <c r="F11" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3615,7 +3618,7 @@
         <v>63</v>
       </c>
       <c r="F14" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3772,7 +3775,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:D1"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5 F3 F7 F9 F13 F15 F17">
+  <conditionalFormatting sqref="F3 F5 F7 F9 F13 F15 F17">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3789,7 +3792,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6 F4 F8 F10 F12 F14 F16">
+  <conditionalFormatting sqref="F4 F6 F8 F10 F12 F14 F16">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3860,14 +3863,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="24"/>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="27"/>
+      <c r="D1" s="29"/>
       <c r="E1" s="8" t="s">
         <v>5</v>
       </c>
@@ -3876,8 +3879,8 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="28"/>
-      <c r="B2" s="29" t="s">
+      <c r="A2" s="27"/>
+      <c r="B2" s="25" t="s">
         <v>149</v>
       </c>
       <c r="C2" s="9" t="s">
@@ -4054,7 +4057,7 @@
         <v>75</v>
       </c>
       <c r="F9" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4174,7 +4177,7 @@
         <v>80</v>
       </c>
       <c r="F14" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4331,7 +4334,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:D1"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5 F3 F7 F9 F13 F15 F17">
+  <conditionalFormatting sqref="F3 F5 F7 F9 F13 F15 F17">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4348,7 +4351,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6 F4 F8 F10 F12 F14 F16">
+  <conditionalFormatting sqref="F4 F6 F8 F10 F12 F14 F16">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4419,14 +4422,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="24"/>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="27"/>
+      <c r="D1" s="29"/>
       <c r="E1" s="8" t="s">
         <v>5</v>
       </c>
@@ -4435,8 +4438,8 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="28"/>
-      <c r="B2" s="29" t="s">
+      <c r="A2" s="27"/>
+      <c r="B2" s="25" t="s">
         <v>149</v>
       </c>
       <c r="C2" s="9" t="s">
@@ -5267,7 +5270,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5 F7 F9 F11 F13 F15 F17 F19 F21 F23 F25 F27 F29">
+  <conditionalFormatting sqref="F7 F5 F9 F11 F13 F15 F17 F19 F21 F23 F25 F27 F29">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5301,7 +5304,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(F34))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4 F6 F8 F10 F12 F14 F16 F18 F20 F22 F24 F26 F28 F30">
+  <conditionalFormatting sqref="F6 F4 F8 F10 F12 F14 F16 F18 F20 F22 F24 F26 F28 F30">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5355,14 +5358,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="24"/>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="27"/>
+      <c r="D1" s="29"/>
       <c r="E1" s="8" t="s">
         <v>5</v>
       </c>
@@ -5371,8 +5374,8 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="28"/>
-      <c r="B2" s="29" t="s">
+      <c r="A2" s="27"/>
+      <c r="B2" s="25" t="s">
         <v>149</v>
       </c>
       <c r="C2" s="9" t="s">
@@ -5826,7 +5829,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:D1"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5 F7 F9 F13 F15 F17 F3">
+  <conditionalFormatting sqref="F7 F5 F9 F13 F15 F17 F3">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5843,7 +5846,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6 F4 F8 F10 F12 F14 F16">
+  <conditionalFormatting sqref="F4 F6 F8 F10 F12 F14 F16">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5914,14 +5917,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="24"/>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="27"/>
+      <c r="D1" s="29"/>
       <c r="E1" s="8" t="s">
         <v>5</v>
       </c>
@@ -5930,8 +5933,8 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="28"/>
-      <c r="B2" s="29" t="s">
+      <c r="A2" s="27"/>
+      <c r="B2" s="25" t="s">
         <v>149</v>
       </c>
       <c r="C2" s="9" t="s">
@@ -6385,7 +6388,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:D1"/>
   </mergeCells>
-  <conditionalFormatting sqref="F7 F5 F9 F13 F15 F17 F3">
+  <conditionalFormatting sqref="F5 F7 F9 F13 F15 F17 F3">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6402,7 +6405,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6 F4 F8 F10 F12 F14 F16">
+  <conditionalFormatting sqref="F4 F6 F8 F10 F12 F14 F16">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
